--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/oct-2026.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/oct-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M246"/>
+  <dimension ref="A1:M247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12310,7 +12310,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2432-721-CM26</t>
+          <t>1078078-3768-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12335,12 +12335,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>69.254.300-9</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12350,12 +12350,12 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>supermercado mayorista metropolitano</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>77.047.926-6</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K190" t="inlineStr"/>
@@ -12365,13 +12365,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>7130.73</v>
+        <v>30227.17</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1078078-3768-CM26</t>
+          <t>2432-721-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.254.300-9</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>supermercado mayorista metropolitano</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>77.047.926-6</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
@@ -12426,7 +12426,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>30227.17</v>
+        <v>7130.73</v>
       </c>
     </row>
     <row r="192">
@@ -12680,7 +12680,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1078078-3757-CM26</t>
+          <t>1078078-3758-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -13119,7 +13119,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1078078-3758-CM26</t>
+          <t>1078078-3757-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -13566,7 +13566,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>5482-217-CM26</t>
+          <t>2432-722-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13591,12 +13591,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>69.070.500-1</t>
+          <t>69.254.300-9</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NUNOA</t>
+          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13606,32 +13606,28 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>COMERCIAL FENIX LTDA</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
-        </is>
-      </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.029.126-9</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>7794.58</v>
+        <v>17326.96</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2432-722-CM26</t>
+          <t>5482-217-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13656,12 +13652,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>69.254.300-9</t>
+          <t>69.070.500-1</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
+          <t>I MUNICIPALIDAD DE NUNOA</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13671,28 +13667,32 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>COMERCIAL FENIX LTDA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>76.029.126-9</t>
-        </is>
-      </c>
-      <c r="K211" t="inlineStr"/>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>17326.96</v>
+        <v>7794.58</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2755-454-CM26</t>
+          <t>2287-816-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13717,27 +13717,27 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>69.253.700-9</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MACUL</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>ADM SPA.</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>77.909.208-9</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -13751,7 +13751,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>1795.56</v>
+        <v>1257.07</v>
       </c>
     </row>
     <row r="213">
@@ -13818,7 +13818,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2287-816-CM26</t>
+          <t>2755-454-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13843,27 +13843,27 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>69.253.700-9</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MACUL</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>ADM SPA.</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.909.208-9</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -13877,13 +13877,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>1257.07</v>
+        <v>1795.56</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1078078-3784-CM26</t>
+          <t>1078078-3787-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13923,12 +13923,12 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>ABATTE OFFICITY</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>96.909.950-0</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
@@ -13938,7 +13938,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>1908.59</v>
+        <v>14204.18</v>
       </c>
     </row>
     <row r="216">
@@ -14253,7 +14253,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1078078-3787-CM26</t>
+          <t>1078078-3784-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -14293,12 +14293,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>ABATTE OFFICITY</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>96.909.950-0</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
@@ -14308,13 +14308,13 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>14204.18</v>
+        <v>1908.59</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1078078-3783-CM26</t>
+          <t>1078078-3782-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -14354,22 +14354,26 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>DISTRIBUIDORA Y COMERCIALIZADORA SANTA ELIANA SPA</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
-        </is>
-      </c>
-      <c r="K222" t="inlineStr"/>
+          <t>77.544.929-2</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>14889.34</v>
+        <v>29592.14</v>
       </c>
     </row>
     <row r="223">
@@ -14696,7 +14700,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1078078-3782-CM26</t>
+          <t>1078078-3783-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14736,26 +14740,22 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIALIZADORA SANTA ELIANA SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>77.544.929-2</t>
-        </is>
-      </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t>O'Higgins</t>
-        </is>
-      </c>
+          <t>76.566.610-4</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr"/>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>29592.14</v>
+        <v>14889.34</v>
       </c>
     </row>
     <row r="229">
@@ -15078,7 +15078,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>1078078-3798-CM26</t>
+          <t>1078078-3800-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -15118,32 +15118,28 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
-        </is>
-      </c>
-      <c r="K234" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.897.437-3</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr"/>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>1024.92</v>
+        <v>8598.77</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1078078-3797-CM26</t>
+          <t>1078078-3798-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -15183,28 +15179,32 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
-        </is>
-      </c>
-      <c r="K235" t="inlineStr"/>
+          <t>15.888.842-4</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>1789.38</v>
+        <v>1024.92</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1078078-3795-CM26</t>
+          <t>1078078-3797-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15244,12 +15244,12 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>FUNDACION VIVIENDA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K236" t="inlineStr"/>
@@ -15259,13 +15259,13 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>24843.56</v>
+        <v>1789.38</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>4236-780-CM26</t>
+          <t>1078078-3795-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15290,47 +15290,43 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>69.160.200-1</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
-        </is>
-      </c>
-      <c r="K237" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>70.016.130-7</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr"/>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>8478.030000000001</v>
+        <v>24843.56</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1078078-3800-CM26</t>
+          <t>4236-780-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -15355,43 +15351,47 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.160.200-1</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
-        </is>
-      </c>
-      <c r="K238" t="inlineStr"/>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>8598.77</v>
+        <v>8478.030000000001</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1078078-3818-CM26</t>
+          <t>1078078-3799-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15406,7 +15406,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -15431,28 +15431,32 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
-        </is>
-      </c>
-      <c r="K239" t="inlineStr"/>
+          <t>76.287.511-k</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>7468.98</v>
+        <v>546.0700000000001</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2546-963-CM26</t>
+          <t>1078078-3818-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15477,47 +15481,43 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
-        </is>
-      </c>
-      <c r="K240" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>11.372.911-2</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr"/>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>33141.83</v>
+        <v>7468.98</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2196-833-CM26</t>
+          <t>2546-963-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15542,43 +15542,47 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>61.608.106-3</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Hospital Psiquiátrico El Peral</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>ALEJANDRO IGLESIAS SOTO</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>8.751.811-6</t>
-        </is>
-      </c>
-      <c r="K241" t="inlineStr"/>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>129.22</v>
+        <v>33141.83</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1285502-27-CM26</t>
+          <t>2196-833-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15603,27 +15607,27 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>61.608.106-3</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>Hospital Psiquiátrico El Peral</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>SOCIEDAD AGRICOLA Y COMERCIAL EL ALMENDRO LIMITADA</t>
+          <t>ALEJANDRO IGLESIAS SOTO</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>76.000.258-5</t>
+          <t>8.751.811-6</t>
         </is>
       </c>
       <c r="K242" t="inlineStr"/>
@@ -15633,13 +15637,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>2458.73</v>
+        <v>129.22</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1078078-3807-CM26</t>
+          <t>1285502-27-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15664,27 +15668,27 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>FUNDACION VIVIENDA</t>
+          <t>SOCIEDAD AGRICOLA Y COMERCIAL EL ALMENDRO LIMITADA</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>76.000.258-5</t>
         </is>
       </c>
       <c r="K243" t="inlineStr"/>
@@ -15694,13 +15698,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>39194.26</v>
+        <v>2458.73</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2403-468-CM26</t>
+          <t>1078078-3807-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15725,12 +15729,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>69.254.000-k</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENALOLEN</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15740,32 +15744,28 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
-        </is>
-      </c>
-      <c r="K244" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>70.016.130-7</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr"/>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>4908.7</v>
+        <v>39194.26</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1057404-1399-CM26</t>
+          <t>2403-468-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15790,27 +15790,27 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>61.602.209-1</t>
+          <t>69.254.000-k</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO HOSPITAL DE ARAUCO</t>
+          <t>I MUNICIPALIDAD DE PENALOLEN</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -15824,71 +15824,136 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>1238.27</v>
+        <v>4908.7</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
+          <t>1057404-1399-CM26</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>61.602.209-1</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARAUCO HOSPITAL DE ARAUCO</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>77.082.051-0</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M246" s="2" t="n">
+        <v>1238.27</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
           <t>1078078-3819-CM26</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>2239-8-LR24</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>oct-2026</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>60.509.001-K</t>
-        </is>
-      </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I246" t="inlineStr">
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>60.509.001-K</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
         <is>
           <t>COMERCIAL ORIONIS SPA</t>
         </is>
       </c>
-      <c r="J246" t="inlineStr">
+      <c r="J247" t="inlineStr">
         <is>
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L246" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M246" s="2" t="n">
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M247" s="2" t="n">
         <v>1271.93</v>
       </c>
     </row>
